--- a/test/test-report-v1.1.0.xlsx
+++ b/test/test-report-v1.1.0.xlsx
@@ -763,11 +763,11 @@
         </is>
       </c>
       <c r="B23" s="8" t="n">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>29.9%</t>
+          <t>23.6%</t>
         </is>
       </c>
     </row>
@@ -778,11 +778,11 @@
         </is>
       </c>
       <c r="B24" s="8" t="n">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>45.4%</t>
         </is>
       </c>
     </row>
@@ -793,11 +793,11 @@
         </is>
       </c>
       <c r="B25" s="8" t="n">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>30.5%</t>
         </is>
       </c>
     </row>
@@ -808,11 +808,11 @@
         </is>
       </c>
       <c r="B26" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.6%</t>
         </is>
       </c>
     </row>
@@ -7393,12 +7393,12 @@
     <row r="133" ht="32" customHeight="1">
       <c r="A133" s="15" t="inlineStr">
         <is>
-          <t>TC-PF-01</t>
+          <t>TC-8.2-01</t>
         </is>
       </c>
       <c r="B133" s="15" t="inlineStr">
         <is>
-          <t>⚡性能测试</t>
+          <t>8.2 后端导出</t>
         </is>
       </c>
       <c r="C133" s="17" t="inlineStr">
@@ -7408,7 +7408,7 @@
       </c>
       <c r="D133" s="14" t="inlineStr">
         <is>
-          <t>搜索 API 延迟 P95&lt;200ms</t>
+          <t>后端导出 PDF</t>
         </is>
       </c>
       <c r="E133" s="15" t="inlineStr">
@@ -7418,17 +7418,17 @@
       </c>
       <c r="F133" s="14" t="inlineStr">
         <is>
-          <t>后端运行中</t>
+          <t>后端运行中, 已登录</t>
         </is>
       </c>
       <c r="G133" s="14" t="inlineStr">
         <is>
-          <t>k6 压测 GET /search/companies</t>
+          <t>POST /api/v1/export format=pdf</t>
         </is>
       </c>
       <c r="H133" s="14" t="inlineStr">
         <is>
-          <t>P95 &lt; 200ms</t>
+          <t>返回taskId, 任务创建成功</t>
         </is>
       </c>
       <c r="I133" s="15" t="inlineStr"/>
@@ -7442,12 +7442,12 @@
     <row r="134" ht="32" customHeight="1">
       <c r="A134" s="15" t="inlineStr">
         <is>
-          <t>TC-PF-02</t>
+          <t>TC-8.2-02</t>
         </is>
       </c>
       <c r="B134" s="15" t="inlineStr">
         <is>
-          <t>⚡性能测试</t>
+          <t>8.2 后端导出</t>
         </is>
       </c>
       <c r="C134" s="17" t="inlineStr">
@@ -7457,7 +7457,7 @@
       </c>
       <c r="D134" s="14" t="inlineStr">
         <is>
-          <t>KPI API 延迟 P95&lt;500ms</t>
+          <t>后端导出 Excel</t>
         </is>
       </c>
       <c r="E134" s="15" t="inlineStr">
@@ -7467,17 +7467,17 @@
       </c>
       <c r="F134" s="14" t="inlineStr">
         <is>
-          <t>后端运行中</t>
+          <t>后端运行中, 已登录</t>
         </is>
       </c>
       <c r="G134" s="14" t="inlineStr">
         <is>
-          <t>k6 压测 GET /reports/{code}/kpi</t>
+          <t>POST /api/v1/export format=xlsx</t>
         </is>
       </c>
       <c r="H134" s="14" t="inlineStr">
         <is>
-          <t>P95 &lt; 500ms</t>
+          <t>返回taskId</t>
         </is>
       </c>
       <c r="I134" s="15" t="inlineStr"/>
@@ -7491,12 +7491,12 @@
     <row r="135" ht="32" customHeight="1">
       <c r="A135" s="15" t="inlineStr">
         <is>
-          <t>TC-PF-03</t>
+          <t>TC-8.2-03</t>
         </is>
       </c>
       <c r="B135" s="15" t="inlineStr">
         <is>
-          <t>⚡性能测试</t>
+          <t>8.2 后端导出</t>
         </is>
       </c>
       <c r="C135" s="17" t="inlineStr">
@@ -7506,7 +7506,7 @@
       </c>
       <c r="D135" s="14" t="inlineStr">
         <is>
-          <t>AI 引擎健康检查 &lt;50ms</t>
+          <t>后端导出 Word</t>
         </is>
       </c>
       <c r="E135" s="15" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="F135" s="14" t="inlineStr">
         <is>
-          <t>AI 引擎运行中</t>
+          <t>后端运行中, 已登录</t>
         </is>
       </c>
       <c r="G135" s="14" t="inlineStr">
         <is>
-          <t>wrk GET /health</t>
+          <t>POST /api/v1/export format=docx</t>
         </is>
       </c>
       <c r="H135" s="14" t="inlineStr">
         <is>
-          <t>P95 &lt; 50ms</t>
+          <t>返回taskId</t>
         </is>
       </c>
       <c r="I135" s="15" t="inlineStr"/>
@@ -7540,22 +7540,22 @@
     <row r="136" ht="32" customHeight="1">
       <c r="A136" s="15" t="inlineStr">
         <is>
-          <t>TC-PF-04</t>
+          <t>TC-8.2-04</t>
         </is>
       </c>
       <c r="B136" s="15" t="inlineStr">
         <is>
-          <t>⚡性能测试</t>
-        </is>
-      </c>
-      <c r="C136" s="18" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>8.2 后端导出</t>
+        </is>
+      </c>
+      <c r="C136" s="17" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D136" s="14" t="inlineStr">
         <is>
-          <t>RAG 检索延迟 &lt;500ms</t>
+          <t>后端导出 PNG</t>
         </is>
       </c>
       <c r="E136" s="15" t="inlineStr">
@@ -7565,17 +7565,17 @@
       </c>
       <c r="F136" s="14" t="inlineStr">
         <is>
-          <t>AI 引擎运行中</t>
+          <t>后端运行中, 已登录</t>
         </is>
       </c>
       <c r="G136" s="14" t="inlineStr">
         <is>
-          <t>POST /ai/v1/rag/search</t>
+          <t>POST /api/v1/export format=png</t>
         </is>
       </c>
       <c r="H136" s="14" t="inlineStr">
         <is>
-          <t>延迟 &lt; 500ms</t>
+          <t>返回taskId</t>
         </is>
       </c>
       <c r="I136" s="15" t="inlineStr"/>
@@ -7589,22 +7589,22 @@
     <row r="137" ht="32" customHeight="1">
       <c r="A137" s="15" t="inlineStr">
         <is>
-          <t>TC-PF-05</t>
+          <t>TC-8.2-05</t>
         </is>
       </c>
       <c r="B137" s="15" t="inlineStr">
         <is>
-          <t>⚡性能测试</t>
-        </is>
-      </c>
-      <c r="C137" s="18" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>8.2 后端导出</t>
+        </is>
+      </c>
+      <c r="C137" s="17" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D137" s="14" t="inlineStr">
         <is>
-          <t>前端首屏 FCP&lt;2s LCP&lt;3s</t>
+          <t>导出含免责声明</t>
         </is>
       </c>
       <c r="E137" s="15" t="inlineStr">
@@ -7614,17 +7614,17 @@
       </c>
       <c r="F137" s="14" t="inlineStr">
         <is>
-          <t>前端运行中</t>
+          <t>后端运行中</t>
         </is>
       </c>
       <c r="G137" s="14" t="inlineStr">
         <is>
-          <t>lighthouse-ci CLI</t>
+          <t>includeDisclaimer=true</t>
         </is>
       </c>
       <c r="H137" s="14" t="inlineStr">
         <is>
-          <t>FCP &lt; 2s, LCP &lt; 3s</t>
+          <t>导出任务创建成功</t>
         </is>
       </c>
       <c r="I137" s="15" t="inlineStr"/>
@@ -7638,22 +7638,22 @@
     <row r="138" ht="32" customHeight="1">
       <c r="A138" s="15" t="inlineStr">
         <is>
-          <t>TC-PF-06</t>
+          <t>TC-8.2-06</t>
         </is>
       </c>
       <c r="B138" s="15" t="inlineStr">
         <is>
-          <t>⚡性能测试</t>
-        </is>
-      </c>
-      <c r="C138" s="18" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>8.2 后端导出</t>
+        </is>
+      </c>
+      <c r="C138" s="17" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D138" s="14" t="inlineStr">
         <is>
-          <t>折线图切换 &lt;200ms</t>
+          <t>无Token导出被拒</t>
         </is>
       </c>
       <c r="E138" s="15" t="inlineStr">
@@ -7663,17 +7663,17 @@
       </c>
       <c r="F138" s="14" t="inlineStr">
         <is>
-          <t>前端运行中</t>
+          <t>后端运行中</t>
         </is>
       </c>
       <c r="G138" s="14" t="inlineStr">
         <is>
-          <t>5 个指标逐一切换计时</t>
+          <t>不带Token请求导出</t>
         </is>
       </c>
       <c r="H138" s="14" t="inlineStr">
         <is>
-          <t>每次 &lt; 200ms</t>
+          <t>返回401</t>
         </is>
       </c>
       <c r="I138" s="15" t="inlineStr"/>
@@ -7687,12 +7687,12 @@
     <row r="139" ht="32" customHeight="1">
       <c r="A139" s="15" t="inlineStr">
         <is>
-          <t>TC-CP-01</t>
+          <t>TC-E2E-01</t>
         </is>
       </c>
       <c r="B139" s="15" t="inlineStr">
         <is>
-          <t>📱兼容性</t>
+          <t>E2E 核心旅程</t>
         </is>
       </c>
       <c r="C139" s="16" t="inlineStr">
@@ -7702,27 +7702,27 @@
       </c>
       <c r="D139" s="14" t="inlineStr">
         <is>
-          <t>Chrome 最新版</t>
+          <t>搜索→看板→聊天完整链路</t>
         </is>
       </c>
       <c r="E139" s="15" t="inlineStr">
         <is>
-          <t>🙋人工</t>
+          <t>🤖自动</t>
         </is>
       </c>
       <c r="F139" s="14" t="inlineStr">
         <is>
-          <t>Windows+Chrome 120+</t>
+          <t>全部服务运行</t>
         </is>
       </c>
       <c r="G139" s="14" t="inlineStr">
         <is>
-          <t>全功能走查</t>
+          <t>搜索茅台→看KPI→切折线图→亮点风险→预测→聊天</t>
         </is>
       </c>
       <c r="H139" s="14" t="inlineStr">
         <is>
-          <t>全部功能正常</t>
+          <t>全链路无报错</t>
         </is>
       </c>
       <c r="I139" s="15" t="inlineStr"/>
@@ -7736,42 +7736,42 @@
     <row r="140" ht="32" customHeight="1">
       <c r="A140" s="15" t="inlineStr">
         <is>
-          <t>TC-CP-02</t>
+          <t>TC-E2E-02</t>
         </is>
       </c>
       <c r="B140" s="15" t="inlineStr">
         <is>
-          <t>📱兼容性</t>
-        </is>
-      </c>
-      <c r="C140" s="17" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>E2E 核心旅程</t>
+        </is>
+      </c>
+      <c r="C140" s="16" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="D140" s="14" t="inlineStr">
         <is>
-          <t>Edge 最新版</t>
+          <t>热门Chip快速分析</t>
         </is>
       </c>
       <c r="E140" s="15" t="inlineStr">
         <is>
-          <t>🙋人工</t>
+          <t>🤖自动</t>
         </is>
       </c>
       <c r="F140" s="14" t="inlineStr">
         <is>
-          <t>Windows+Edge 120+</t>
+          <t>全部服务运行</t>
         </is>
       </c>
       <c r="G140" s="14" t="inlineStr">
         <is>
-          <t>全功能走查</t>
+          <t>点击宁德时代Chip→看Dashboard→切换工商银行</t>
         </is>
       </c>
       <c r="H140" s="14" t="inlineStr">
         <is>
-          <t>全部功能正常</t>
+          <t>跳转正确，数据加载正常</t>
         </is>
       </c>
       <c r="I140" s="15" t="inlineStr"/>
@@ -7785,42 +7785,42 @@
     <row r="141" ht="32" customHeight="1">
       <c r="A141" s="15" t="inlineStr">
         <is>
-          <t>TC-CP-03</t>
+          <t>TC-E2E-03</t>
         </is>
       </c>
       <c r="B141" s="15" t="inlineStr">
         <is>
-          <t>📱兼容性</t>
-        </is>
-      </c>
-      <c r="C141" s="18" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>E2E 核心旅程</t>
+        </is>
+      </c>
+      <c r="C141" s="16" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="D141" s="14" t="inlineStr">
         <is>
-          <t>移动端 Safari</t>
+          <t>历史记录+导出</t>
         </is>
       </c>
       <c r="E141" s="15" t="inlineStr">
         <is>
-          <t>🙋人工</t>
+          <t>🤖自动</t>
         </is>
       </c>
       <c r="F141" s="14" t="inlineStr">
         <is>
-          <t>iOS Safari 真机</t>
+          <t>全部服务运行</t>
         </is>
       </c>
       <c r="G141" s="14" t="inlineStr">
         <is>
-          <t>搜索/看板/聊天可用</t>
+          <t>分析3家公司→看历史→点击切换→导出PNG→导出Excel</t>
         </is>
       </c>
       <c r="H141" s="14" t="inlineStr">
         <is>
-          <t>布局自适应</t>
+          <t>历史正确，导出正常</t>
         </is>
       </c>
       <c r="I141" s="15" t="inlineStr"/>
@@ -7834,42 +7834,42 @@
     <row r="142" ht="32" customHeight="1">
       <c r="A142" s="15" t="inlineStr">
         <is>
-          <t>TC-CP-04</t>
+          <t>TC-E2E-04</t>
         </is>
       </c>
       <c r="B142" s="15" t="inlineStr">
         <is>
-          <t>📱兼容性</t>
-        </is>
-      </c>
-      <c r="C142" s="18" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>E2E 核心旅程</t>
+        </is>
+      </c>
+      <c r="C142" s="17" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D142" s="14" t="inlineStr">
         <is>
-          <t>移动端 Chrome</t>
+          <t>无匹配→重试</t>
         </is>
       </c>
       <c r="E142" s="15" t="inlineStr">
         <is>
-          <t>🙋人工</t>
+          <t>🤖自动</t>
         </is>
       </c>
       <c r="F142" s="14" t="inlineStr">
         <is>
-          <t>Android Chrome 真机</t>
+          <t>全部服务运行</t>
         </is>
       </c>
       <c r="G142" s="14" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>搜'xyzabc'→确认空状态→搜'600519'</t>
         </is>
       </c>
       <c r="H142" s="14" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>空状态友好，搜索恢复</t>
         </is>
       </c>
       <c r="I142" s="15" t="inlineStr"/>
@@ -7883,42 +7883,42 @@
     <row r="143" ht="32" customHeight="1">
       <c r="A143" s="15" t="inlineStr">
         <is>
-          <t>TC-CP-05</t>
+          <t>TC-PF-01</t>
         </is>
       </c>
       <c r="B143" s="15" t="inlineStr">
         <is>
-          <t>📱兼容性</t>
-        </is>
-      </c>
-      <c r="C143" s="16" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>⚡性能测试</t>
+        </is>
+      </c>
+      <c r="C143" s="17" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D143" s="14" t="inlineStr">
         <is>
-          <t>1920×1080 桌面布局</t>
+          <t>搜索 API 延迟 P95&lt;200ms</t>
         </is>
       </c>
       <c r="E143" s="15" t="inlineStr">
         <is>
-          <t>🙋人工</t>
+          <t>🤖自动</t>
         </is>
       </c>
       <c r="F143" s="14" t="inlineStr">
         <is>
-          <t>标准桌面分辨率</t>
+          <t>后端运行中</t>
         </is>
       </c>
       <c r="G143" s="14" t="inlineStr">
         <is>
-          <t>检查页面布局</t>
+          <t>k6 压测 GET /search/companies</t>
         </is>
       </c>
       <c r="H143" s="14" t="inlineStr">
         <is>
-          <t>布局正常</t>
+          <t>P95 &lt; 200ms</t>
         </is>
       </c>
       <c r="I143" s="15" t="inlineStr"/>
@@ -7932,42 +7932,42 @@
     <row r="144" ht="32" customHeight="1">
       <c r="A144" s="15" t="inlineStr">
         <is>
-          <t>TC-CP-06</t>
+          <t>TC-PF-02</t>
         </is>
       </c>
       <c r="B144" s="15" t="inlineStr">
         <is>
-          <t>📱兼容性</t>
-        </is>
-      </c>
-      <c r="C144" s="18" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>⚡性能测试</t>
+        </is>
+      </c>
+      <c r="C144" s="17" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D144" s="14" t="inlineStr">
         <is>
-          <t>375×812 iPhone X 布局</t>
+          <t>KPI API 延迟 P95&lt;500ms</t>
         </is>
       </c>
       <c r="E144" s="15" t="inlineStr">
         <is>
-          <t>🙋人工</t>
+          <t>🤖自动</t>
         </is>
       </c>
       <c r="F144" s="14" t="inlineStr">
         <is>
-          <t>DevTools 模拟</t>
+          <t>后端运行中</t>
         </is>
       </c>
       <c r="G144" s="14" t="inlineStr">
         <is>
-          <t>检查移动端布局</t>
+          <t>k6 压测 GET /reports/{code}/kpi</t>
         </is>
       </c>
       <c r="H144" s="14" t="inlineStr">
         <is>
-          <t>1 列布局，横向滚动表格</t>
+          <t>P95 &lt; 500ms</t>
         </is>
       </c>
       <c r="I144" s="15" t="inlineStr"/>
@@ -7981,22 +7981,22 @@
     <row r="145" ht="32" customHeight="1">
       <c r="A145" s="15" t="inlineStr">
         <is>
-          <t>TC-SC-01</t>
+          <t>TC-PF-03</t>
         </is>
       </c>
       <c r="B145" s="15" t="inlineStr">
         <is>
-          <t>🔒安全测试</t>
-        </is>
-      </c>
-      <c r="C145" s="18" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>⚡性能测试</t>
+        </is>
+      </c>
+      <c r="C145" s="17" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D145" s="14" t="inlineStr">
         <is>
-          <t>SQL 注入防护</t>
+          <t>AI 引擎健康检查 &lt;50ms</t>
         </is>
       </c>
       <c r="E145" s="15" t="inlineStr">
@@ -8006,17 +8006,17 @@
       </c>
       <c r="F145" s="14" t="inlineStr">
         <is>
-          <t>后端运行中</t>
+          <t>AI 引擎运行中</t>
         </is>
       </c>
       <c r="G145" s="14" t="inlineStr">
         <is>
-          <t>搜索框输入 'OR'1'='1</t>
+          <t>wrk GET /health</t>
         </is>
       </c>
       <c r="H145" s="14" t="inlineStr">
         <is>
-          <t>不返回异常数据</t>
+          <t>P95 &lt; 50ms</t>
         </is>
       </c>
       <c r="I145" s="15" t="inlineStr"/>
@@ -8030,12 +8030,12 @@
     <row r="146" ht="32" customHeight="1">
       <c r="A146" s="15" t="inlineStr">
         <is>
-          <t>TC-SC-02</t>
+          <t>TC-PF-04</t>
         </is>
       </c>
       <c r="B146" s="15" t="inlineStr">
         <is>
-          <t>🔒安全测试</t>
+          <t>⚡性能测试</t>
         </is>
       </c>
       <c r="C146" s="18" t="inlineStr">
@@ -8045,7 +8045,7 @@
       </c>
       <c r="D146" s="14" t="inlineStr">
         <is>
-          <t>XSS 防护</t>
+          <t>RAG 检索延迟 &lt;500ms</t>
         </is>
       </c>
       <c r="E146" s="15" t="inlineStr">
@@ -8055,17 +8055,17 @@
       </c>
       <c r="F146" s="14" t="inlineStr">
         <is>
-          <t>后端运行中</t>
+          <t>AI 引擎运行中</t>
         </is>
       </c>
       <c r="G146" s="14" t="inlineStr">
         <is>
-          <t>输入 &lt;script&gt;alert(1)&lt;/script&gt;</t>
+          <t>POST /ai/v1/rag/search</t>
         </is>
       </c>
       <c r="H146" s="14" t="inlineStr">
         <is>
-          <t>不执行脚本</t>
+          <t>延迟 &lt; 500ms</t>
         </is>
       </c>
       <c r="I146" s="15" t="inlineStr"/>
@@ -8079,12 +8079,12 @@
     <row r="147" ht="32" customHeight="1">
       <c r="A147" s="15" t="inlineStr">
         <is>
-          <t>TC-SC-03</t>
+          <t>TC-PF-05</t>
         </is>
       </c>
       <c r="B147" s="15" t="inlineStr">
         <is>
-          <t>🔒安全测试</t>
+          <t>⚡性能测试</t>
         </is>
       </c>
       <c r="C147" s="18" t="inlineStr">
@@ -8094,7 +8094,7 @@
       </c>
       <c r="D147" s="14" t="inlineStr">
         <is>
-          <t>超大文件拦截</t>
+          <t>前端首屏 FCP&lt;2s LCP&lt;3s</t>
         </is>
       </c>
       <c r="E147" s="15" t="inlineStr">
@@ -8104,17 +8104,17 @@
       </c>
       <c r="F147" s="14" t="inlineStr">
         <is>
-          <t>后端运行中</t>
+          <t>前端运行中</t>
         </is>
       </c>
       <c r="G147" s="14" t="inlineStr">
         <is>
-          <t>上传 &gt;50MB 文件</t>
+          <t>lighthouse-ci CLI</t>
         </is>
       </c>
       <c r="H147" s="14" t="inlineStr">
         <is>
-          <t>前端拦截</t>
+          <t>FCP &lt; 2s, LCP &lt; 3s</t>
         </is>
       </c>
       <c r="I147" s="15" t="inlineStr"/>
@@ -8128,22 +8128,22 @@
     <row r="148" ht="32" customHeight="1">
       <c r="A148" s="15" t="inlineStr">
         <is>
-          <t>TC-SC-04</t>
+          <t>TC-PF-06</t>
         </is>
       </c>
       <c r="B148" s="15" t="inlineStr">
         <is>
-          <t>🔒安全测试</t>
-        </is>
-      </c>
-      <c r="C148" s="17" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>⚡性能测试</t>
+        </is>
+      </c>
+      <c r="C148" s="18" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D148" s="14" t="inlineStr">
         <is>
-          <t>🔒 未授权访问 401</t>
+          <t>折线图切换 &lt;200ms</t>
         </is>
       </c>
       <c r="E148" s="15" t="inlineStr">
@@ -8153,17 +8153,17 @@
       </c>
       <c r="F148" s="14" t="inlineStr">
         <is>
-          <t>JWT 已实施</t>
+          <t>前端运行中</t>
         </is>
       </c>
       <c r="G148" s="14" t="inlineStr">
         <is>
-          <t>不带 Token 访问 /api/v1/history</t>
+          <t>5 个指标逐一切换计时</t>
         </is>
       </c>
       <c r="H148" s="14" t="inlineStr">
         <is>
-          <t>返回 401</t>
+          <t>每次 &lt; 200ms</t>
         </is>
       </c>
       <c r="I148" s="15" t="inlineStr"/>
@@ -8177,42 +8177,42 @@
     <row r="149" ht="32" customHeight="1">
       <c r="A149" s="15" t="inlineStr">
         <is>
-          <t>TC-SC-05</t>
+          <t>TC-CP-01</t>
         </is>
       </c>
       <c r="B149" s="15" t="inlineStr">
         <is>
-          <t>🔒安全测试</t>
-        </is>
-      </c>
-      <c r="C149" s="17" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>📱兼容性</t>
+        </is>
+      </c>
+      <c r="C149" s="16" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="D149" s="14" t="inlineStr">
         <is>
-          <t>🔒 伪造 Token 被拒</t>
+          <t>Chrome 最新版</t>
         </is>
       </c>
       <c r="E149" s="15" t="inlineStr">
         <is>
-          <t>🤖自动</t>
+          <t>🙋人工</t>
         </is>
       </c>
       <c r="F149" s="14" t="inlineStr">
         <is>
-          <t>后端运行中</t>
+          <t>Windows+Chrome 120+</t>
         </is>
       </c>
       <c r="G149" s="14" t="inlineStr">
         <is>
-          <t>带 Authorization: Bearer fake-token</t>
+          <t>全功能走查</t>
         </is>
       </c>
       <c r="H149" s="14" t="inlineStr">
         <is>
-          <t>返回 401</t>
+          <t>全部功能正常</t>
         </is>
       </c>
       <c r="I149" s="15" t="inlineStr"/>
@@ -8226,42 +8226,42 @@
     <row r="150" ht="32" customHeight="1">
       <c r="A150" s="15" t="inlineStr">
         <is>
-          <t>TC-SC-06</t>
+          <t>TC-CP-02</t>
         </is>
       </c>
       <c r="B150" s="15" t="inlineStr">
         <is>
-          <t>🔒安全测试</t>
-        </is>
-      </c>
-      <c r="C150" s="18" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>📱兼容性</t>
+        </is>
+      </c>
+      <c r="C150" s="17" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D150" s="14" t="inlineStr">
         <is>
-          <t>🔒 过期 Token 被拒</t>
+          <t>Edge 最新版</t>
         </is>
       </c>
       <c r="E150" s="15" t="inlineStr">
         <is>
-          <t>🤖自动</t>
+          <t>🙋人工</t>
         </is>
       </c>
       <c r="F150" s="14" t="inlineStr">
         <is>
-          <t>后端运行中</t>
+          <t>Windows+Edge 120+</t>
         </is>
       </c>
       <c r="G150" s="14" t="inlineStr">
         <is>
-          <t>带已过期 Token</t>
+          <t>全功能走查</t>
         </is>
       </c>
       <c r="H150" s="14" t="inlineStr">
         <is>
-          <t>返回 401</t>
+          <t>全部功能正常</t>
         </is>
       </c>
       <c r="I150" s="15" t="inlineStr"/>
@@ -8275,42 +8275,42 @@
     <row r="151" ht="32" customHeight="1">
       <c r="A151" s="15" t="inlineStr">
         <is>
-          <t>TC-9.1-01</t>
+          <t>TC-CP-03</t>
         </is>
       </c>
       <c r="B151" s="15" t="inlineStr">
         <is>
-          <t>9.1 注册登录 API</t>
-        </is>
-      </c>
-      <c r="C151" s="16" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>📱兼容性</t>
+        </is>
+      </c>
+      <c r="C151" s="18" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D151" s="14" t="inlineStr">
         <is>
-          <t>注册新用户</t>
+          <t>移动端 Safari</t>
         </is>
       </c>
       <c r="E151" s="15" t="inlineStr">
         <is>
-          <t>🤖自动</t>
+          <t>🙋人工</t>
         </is>
       </c>
       <c r="F151" s="14" t="inlineStr">
         <is>
-          <t>后端运行中</t>
+          <t>iOS Safari 真机</t>
         </is>
       </c>
       <c r="G151" s="14" t="inlineStr">
         <is>
-          <t>POST /api/v1/auth/register</t>
+          <t>搜索/看板/聊天可用</t>
         </is>
       </c>
       <c r="H151" s="14" t="inlineStr">
         <is>
-          <t>code=0, 返回 userId+email+nickname</t>
+          <t>布局自适应</t>
         </is>
       </c>
       <c r="I151" s="15" t="inlineStr"/>
@@ -8324,42 +8324,42 @@
     <row r="152" ht="32" customHeight="1">
       <c r="A152" s="15" t="inlineStr">
         <is>
-          <t>TC-9.1-02</t>
+          <t>TC-CP-04</t>
         </is>
       </c>
       <c r="B152" s="15" t="inlineStr">
         <is>
-          <t>9.1 注册登录 API</t>
-        </is>
-      </c>
-      <c r="C152" s="16" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>📱兼容性</t>
+        </is>
+      </c>
+      <c r="C152" s="18" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D152" s="14" t="inlineStr">
         <is>
-          <t>重复注册拦截</t>
+          <t>移动端 Chrome</t>
         </is>
       </c>
       <c r="E152" s="15" t="inlineStr">
         <is>
-          <t>🤖自动</t>
+          <t>🙋人工</t>
         </is>
       </c>
       <c r="F152" s="14" t="inlineStr">
         <is>
-          <t>已注册</t>
+          <t>Android Chrome 真机</t>
         </is>
       </c>
       <c r="G152" s="14" t="inlineStr">
         <is>
-          <t>再次注册相同邮箱</t>
+          <t>同上</t>
         </is>
       </c>
       <c r="H152" s="14" t="inlineStr">
         <is>
-          <t>code≠0, 提示邮箱已注册</t>
+          <t>同上</t>
         </is>
       </c>
       <c r="I152" s="15" t="inlineStr"/>
@@ -8373,42 +8373,42 @@
     <row r="153" ht="32" customHeight="1">
       <c r="A153" s="15" t="inlineStr">
         <is>
-          <t>TC-9.1-03</t>
+          <t>TC-CP-05</t>
         </is>
       </c>
       <c r="B153" s="15" t="inlineStr">
         <is>
-          <t>9.1 注册登录 API</t>
-        </is>
-      </c>
-      <c r="C153" s="17" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>📱兼容性</t>
+        </is>
+      </c>
+      <c r="C153" s="16" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="D153" s="14" t="inlineStr">
         <is>
-          <t>密码过短拦截</t>
+          <t>1920×1080 桌面布局</t>
         </is>
       </c>
       <c r="E153" s="15" t="inlineStr">
         <is>
-          <t>🤖自动</t>
+          <t>🙋人工</t>
         </is>
       </c>
       <c r="F153" s="14" t="inlineStr">
         <is>
-          <t>后端运行中</t>
+          <t>标准桌面分辨率</t>
         </is>
       </c>
       <c r="G153" s="14" t="inlineStr">
         <is>
-          <t>注册 password='123'</t>
+          <t>检查页面布局</t>
         </is>
       </c>
       <c r="H153" s="14" t="inlineStr">
         <is>
-          <t>code≠0, 提示密码至少6位</t>
+          <t>布局正常</t>
         </is>
       </c>
       <c r="I153" s="15" t="inlineStr"/>
@@ -8422,42 +8422,42 @@
     <row r="154" ht="32" customHeight="1">
       <c r="A154" s="15" t="inlineStr">
         <is>
-          <t>TC-9.1-04</t>
+          <t>TC-CP-06</t>
         </is>
       </c>
       <c r="B154" s="15" t="inlineStr">
         <is>
-          <t>9.1 注册登录 API</t>
-        </is>
-      </c>
-      <c r="C154" s="17" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>📱兼容性</t>
+        </is>
+      </c>
+      <c r="C154" s="18" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D154" s="14" t="inlineStr">
         <is>
-          <t>邮箱格式校验</t>
+          <t>375×812 iPhone X 布局</t>
         </is>
       </c>
       <c r="E154" s="15" t="inlineStr">
         <is>
-          <t>🤖自动</t>
+          <t>🙋人工</t>
         </is>
       </c>
       <c r="F154" s="14" t="inlineStr">
         <is>
-          <t>后端运行中</t>
+          <t>DevTools 模拟</t>
         </is>
       </c>
       <c r="G154" s="14" t="inlineStr">
         <is>
-          <t>注册 email='not-email'</t>
+          <t>检查移动端布局</t>
         </is>
       </c>
       <c r="H154" s="14" t="inlineStr">
         <is>
-          <t>code≠0 提示格式不正确</t>
+          <t>1 列布局，横向滚动表格</t>
         </is>
       </c>
       <c r="I154" s="15" t="inlineStr"/>
@@ -8471,22 +8471,22 @@
     <row r="155" ht="32" customHeight="1">
       <c r="A155" s="15" t="inlineStr">
         <is>
-          <t>TC-9.1-05</t>
+          <t>TC-SC-01</t>
         </is>
       </c>
       <c r="B155" s="15" t="inlineStr">
         <is>
-          <t>9.1 注册登录 API</t>
-        </is>
-      </c>
-      <c r="C155" s="16" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>🔒安全测试</t>
+        </is>
+      </c>
+      <c r="C155" s="18" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D155" s="14" t="inlineStr">
         <is>
-          <t>登录获取 Token</t>
+          <t>SQL 注入防护</t>
         </is>
       </c>
       <c r="E155" s="15" t="inlineStr">
@@ -8496,17 +8496,17 @@
       </c>
       <c r="F155" s="14" t="inlineStr">
         <is>
-          <t>已注册用户</t>
+          <t>后端运行中</t>
         </is>
       </c>
       <c r="G155" s="14" t="inlineStr">
         <is>
-          <t>POST /api/v1/auth/login</t>
+          <t>搜索框输入 'OR'1'='1</t>
         </is>
       </c>
       <c r="H155" s="14" t="inlineStr">
         <is>
-          <t>返回 accessToken(2h)+refreshToken(7d)</t>
+          <t>不返回异常数据</t>
         </is>
       </c>
       <c r="I155" s="15" t="inlineStr"/>
@@ -8520,22 +8520,22 @@
     <row r="156" ht="32" customHeight="1">
       <c r="A156" s="15" t="inlineStr">
         <is>
-          <t>TC-9.1-06</t>
+          <t>TC-SC-02</t>
         </is>
       </c>
       <c r="B156" s="15" t="inlineStr">
         <is>
-          <t>9.1 注册登录 API</t>
-        </is>
-      </c>
-      <c r="C156" s="16" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>🔒安全测试</t>
+        </is>
+      </c>
+      <c r="C156" s="18" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D156" s="14" t="inlineStr">
         <is>
-          <t>错误密码登录</t>
+          <t>XSS 防护</t>
         </is>
       </c>
       <c r="E156" s="15" t="inlineStr">
@@ -8545,17 +8545,17 @@
       </c>
       <c r="F156" s="14" t="inlineStr">
         <is>
-          <t>已注册用户</t>
+          <t>后端运行中</t>
         </is>
       </c>
       <c r="G156" s="14" t="inlineStr">
         <is>
-          <t>登录 password='wrong'</t>
+          <t>输入 &lt;script&gt;alert(1)&lt;/script&gt;</t>
         </is>
       </c>
       <c r="H156" s="14" t="inlineStr">
         <is>
-          <t>code≠0, 提示邮箱或密码错误</t>
+          <t>不执行脚本</t>
         </is>
       </c>
       <c r="I156" s="15" t="inlineStr"/>
@@ -8569,22 +8569,22 @@
     <row r="157" ht="32" customHeight="1">
       <c r="A157" s="15" t="inlineStr">
         <is>
-          <t>TC-9.1-07</t>
+          <t>TC-SC-03</t>
         </is>
       </c>
       <c r="B157" s="15" t="inlineStr">
         <is>
-          <t>9.1 注册登录 API</t>
-        </is>
-      </c>
-      <c r="C157" s="17" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>🔒安全测试</t>
+        </is>
+      </c>
+      <c r="C157" s="18" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D157" s="14" t="inlineStr">
         <is>
-          <t>刷新 Token</t>
+          <t>超大文件拦截</t>
         </is>
       </c>
       <c r="E157" s="15" t="inlineStr">
@@ -8594,17 +8594,17 @@
       </c>
       <c r="F157" s="14" t="inlineStr">
         <is>
-          <t>已登录,有 refreshToken</t>
+          <t>后端运行中</t>
         </is>
       </c>
       <c r="G157" s="14" t="inlineStr">
         <is>
-          <t>POST /api/v1/auth/refresh</t>
+          <t>上传 &gt;50MB 文件</t>
         </is>
       </c>
       <c r="H157" s="14" t="inlineStr">
         <is>
-          <t>返回新 accessToken+refreshToken</t>
+          <t>前端拦截</t>
         </is>
       </c>
       <c r="I157" s="15" t="inlineStr"/>
@@ -8618,22 +8618,22 @@
     <row r="158" ht="32" customHeight="1">
       <c r="A158" s="15" t="inlineStr">
         <is>
-          <t>TC-9.1-08</t>
+          <t>TC-SC-04</t>
         </is>
       </c>
       <c r="B158" s="15" t="inlineStr">
         <is>
-          <t>9.1 注册登录 API</t>
-        </is>
-      </c>
-      <c r="C158" s="17" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>🔒安全测试</t>
+        </is>
+      </c>
+      <c r="C158" s="18" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D158" s="14" t="inlineStr">
         <is>
-          <t>过期 Token 自动刷新</t>
+          <t>未授权访问 401（预留）</t>
         </is>
       </c>
       <c r="E158" s="15" t="inlineStr">
@@ -8643,17 +8643,17 @@
       </c>
       <c r="F158" s="14" t="inlineStr">
         <is>
-          <t>accessToken 过期</t>
+          <t>JWT 实施后</t>
         </is>
       </c>
       <c r="G158" s="14" t="inlineStr">
         <is>
-          <t>前端自动调 refresh</t>
+          <t>不带 Token 访问 🔒 接口</t>
         </is>
       </c>
       <c r="H158" s="14" t="inlineStr">
         <is>
-          <t>无感刷新，请求正常</t>
+          <t>返回 401</t>
         </is>
       </c>
       <c r="I158" s="15" t="inlineStr"/>
@@ -8667,22 +8667,22 @@
     <row r="159" ht="32" customHeight="1">
       <c r="A159" s="15" t="inlineStr">
         <is>
-          <t>TC-9.1-09</t>
+          <t>TC-SC-05</t>
         </is>
       </c>
       <c r="B159" s="15" t="inlineStr">
         <is>
-          <t>9.1 注册登录 API</t>
-        </is>
-      </c>
-      <c r="C159" s="17" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>🔒安全测试</t>
+        </is>
+      </c>
+      <c r="C159" s="18" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D159" s="14" t="inlineStr">
         <is>
-          <t>登出加入黑名单</t>
+          <t>伪造 Token 拒绝</t>
         </is>
       </c>
       <c r="E159" s="15" t="inlineStr">
@@ -8692,17 +8692,17 @@
       </c>
       <c r="F159" s="14" t="inlineStr">
         <is>
-          <t>已登录</t>
+          <t>后端运行中</t>
         </is>
       </c>
       <c r="G159" s="14" t="inlineStr">
         <is>
-          <t>POST /api/v1/auth/logout</t>
+          <t>带伪造 Token 访问 🔒 接口</t>
         </is>
       </c>
       <c r="H159" s="14" t="inlineStr">
         <is>
-          <t>code=0, 旧 Token 无法再使用</t>
+          <t>返回 401</t>
         </is>
       </c>
       <c r="I159" s="15" t="inlineStr"/>
@@ -8716,22 +8716,22 @@
     <row r="160" ht="32" customHeight="1">
       <c r="A160" s="15" t="inlineStr">
         <is>
-          <t>TC-9.1-10</t>
+          <t>TC-9.1-01</t>
         </is>
       </c>
       <c r="B160" s="15" t="inlineStr">
         <is>
-          <t>9.1 注册登录 API</t>
-        </is>
-      </c>
-      <c r="C160" s="17" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>9.1 认证 API</t>
+        </is>
+      </c>
+      <c r="C160" s="18" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D160" s="14" t="inlineStr">
         <is>
-          <t>获取当前用户</t>
+          <t>用户注册</t>
         </is>
       </c>
       <c r="E160" s="15" t="inlineStr">
@@ -8741,12 +8741,12 @@
       </c>
       <c r="F160" s="14" t="inlineStr">
         <is>
-          <t>已登录</t>
+          <t>后端运行中</t>
         </is>
       </c>
       <c r="G160" s="14" t="inlineStr">
         <is>
-          <t>GET /api/v1/auth/me</t>
+          <t>POST /api/v1/auth/register</t>
         </is>
       </c>
       <c r="H160" s="14" t="inlineStr">
@@ -8765,22 +8765,22 @@
     <row r="161" ht="32" customHeight="1">
       <c r="A161" s="15" t="inlineStr">
         <is>
-          <t>TC-9.2-01</t>
+          <t>TC-9.1-02</t>
         </is>
       </c>
       <c r="B161" s="15" t="inlineStr">
         <is>
-          <t>9.2 路由守卫 UI</t>
-        </is>
-      </c>
-      <c r="C161" s="16" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>9.1 认证 API</t>
+        </is>
+      </c>
+      <c r="C161" s="18" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D161" s="14" t="inlineStr">
         <is>
-          <t>未登录访问 /search 重定向</t>
+          <t>重复注册拦截</t>
         </is>
       </c>
       <c r="E161" s="15" t="inlineStr">
@@ -8790,17 +8790,17 @@
       </c>
       <c r="F161" s="14" t="inlineStr">
         <is>
-          <t>未登录</t>
+          <t>后端运行中</t>
         </is>
       </c>
       <c r="G161" s="14" t="inlineStr">
         <is>
-          <t>直接访问 /search</t>
+          <t>重复注册相同 email</t>
         </is>
       </c>
       <c r="H161" s="14" t="inlineStr">
         <is>
-          <t>重定向到 /login?redirect=/search</t>
+          <t>被拦截</t>
         </is>
       </c>
       <c r="I161" s="15" t="inlineStr"/>
@@ -8814,22 +8814,22 @@
     <row r="162" ht="32" customHeight="1">
       <c r="A162" s="15" t="inlineStr">
         <is>
-          <t>TC-9.2-02</t>
+          <t>TC-9.1-03</t>
         </is>
       </c>
       <c r="B162" s="15" t="inlineStr">
         <is>
-          <t>9.2 路由守卫 UI</t>
-        </is>
-      </c>
-      <c r="C162" s="16" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>9.1 认证 API</t>
+        </is>
+      </c>
+      <c r="C162" s="18" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D162" s="14" t="inlineStr">
         <is>
-          <t>未登录访问 Dashboard 重定向</t>
+          <t>弱密码拦截</t>
         </is>
       </c>
       <c r="E162" s="15" t="inlineStr">
@@ -8839,17 +8839,17 @@
       </c>
       <c r="F162" s="14" t="inlineStr">
         <is>
-          <t>未登录</t>
+          <t>后端运行中</t>
         </is>
       </c>
       <c r="G162" s="14" t="inlineStr">
         <is>
-          <t>直接访问 /dashboard/600519</t>
+          <t>密码过短注册</t>
         </is>
       </c>
       <c r="H162" s="14" t="inlineStr">
         <is>
-          <t>重定向到 /login</t>
+          <t>返回400</t>
         </is>
       </c>
       <c r="I162" s="15" t="inlineStr"/>
@@ -8863,22 +8863,22 @@
     <row r="163" ht="32" customHeight="1">
       <c r="A163" s="15" t="inlineStr">
         <is>
-          <t>TC-9.2-03</t>
+          <t>TC-9.1-05</t>
         </is>
       </c>
       <c r="B163" s="15" t="inlineStr">
         <is>
-          <t>9.2 路由守卫 UI</t>
-        </is>
-      </c>
-      <c r="C163" s="16" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>9.1 认证 API</t>
+        </is>
+      </c>
+      <c r="C163" s="18" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D163" s="14" t="inlineStr">
         <is>
-          <t>登录后自动跳回</t>
+          <t>登录成功返回JWT</t>
         </is>
       </c>
       <c r="E163" s="15" t="inlineStr">
@@ -8888,17 +8888,17 @@
       </c>
       <c r="F163" s="14" t="inlineStr">
         <is>
-          <t>已注册</t>
+          <t>后端运行中</t>
         </is>
       </c>
       <c r="G163" s="14" t="inlineStr">
         <is>
-          <t>登录 → 自动跳转 redirect 参数目标</t>
+          <t>POST /api/v1/auth/login</t>
         </is>
       </c>
       <c r="H163" s="14" t="inlineStr">
         <is>
-          <t>跳回 /search 或指定页面</t>
+          <t>返回 accessToken+refreshToken</t>
         </is>
       </c>
       <c r="I163" s="15" t="inlineStr"/>
@@ -8912,22 +8912,22 @@
     <row r="164" ht="32" customHeight="1">
       <c r="A164" s="15" t="inlineStr">
         <is>
-          <t>TC-9.2-04</t>
+          <t>TC-9.1-06</t>
         </is>
       </c>
       <c r="B164" s="15" t="inlineStr">
         <is>
-          <t>9.2 路由守卫 UI</t>
-        </is>
-      </c>
-      <c r="C164" s="17" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>9.1 认证 API</t>
+        </is>
+      </c>
+      <c r="C164" s="18" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D164" s="14" t="inlineStr">
         <is>
-          <t>已登录访问 /login 重定向</t>
+          <t>错误密码拒绝</t>
         </is>
       </c>
       <c r="E164" s="15" t="inlineStr">
@@ -8937,17 +8937,17 @@
       </c>
       <c r="F164" s="14" t="inlineStr">
         <is>
-          <t>已登录</t>
+          <t>后端运行中</t>
         </is>
       </c>
       <c r="G164" s="14" t="inlineStr">
         <is>
-          <t>访问 /login</t>
+          <t>错误密码登录</t>
         </is>
       </c>
       <c r="H164" s="14" t="inlineStr">
         <is>
-          <t>重定向到 /search</t>
+          <t>返回400</t>
         </is>
       </c>
       <c r="I164" s="15" t="inlineStr"/>
@@ -8961,42 +8961,42 @@
     <row r="165" ht="32" customHeight="1">
       <c r="A165" s="15" t="inlineStr">
         <is>
-          <t>TC-9.2-05</t>
+          <t>TC-9.1-09</t>
         </is>
       </c>
       <c r="B165" s="15" t="inlineStr">
         <is>
-          <t>9.2 路由守卫 UI</t>
-        </is>
-      </c>
-      <c r="C165" s="16" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>9.1 认证 API</t>
+        </is>
+      </c>
+      <c r="C165" s="18" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D165" s="14" t="inlineStr">
         <is>
-          <t>Navbar 显示登录按钮(未登录)</t>
+          <t>登出成功</t>
         </is>
       </c>
       <c r="E165" s="15" t="inlineStr">
         <is>
-          <t>🙋人工</t>
+          <t>🤖自动</t>
         </is>
       </c>
       <c r="F165" s="14" t="inlineStr">
         <is>
-          <t>未登录</t>
+          <t>后端运行中, 已登录</t>
         </is>
       </c>
       <c r="G165" s="14" t="inlineStr">
         <is>
-          <t>查看 Navbar</t>
+          <t>POST /api/v1/auth/logout</t>
         </is>
       </c>
       <c r="H165" s="14" t="inlineStr">
         <is>
-          <t>显示 '🔑 登录' 按钮</t>
+          <t>code=0</t>
         </is>
       </c>
       <c r="I165" s="15" t="inlineStr"/>
@@ -9010,42 +9010,42 @@
     <row r="166" ht="32" customHeight="1">
       <c r="A166" s="15" t="inlineStr">
         <is>
-          <t>TC-9.2-06</t>
+          <t>TC-9.1-10</t>
         </is>
       </c>
       <c r="B166" s="15" t="inlineStr">
         <is>
-          <t>9.2 路由守卫 UI</t>
-        </is>
-      </c>
-      <c r="C166" s="16" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>9.1 认证 API</t>
+        </is>
+      </c>
+      <c r="C166" s="18" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D166" s="14" t="inlineStr">
         <is>
-          <t>Navbar 显示用户信息(已登录)</t>
+          <t>获取当前用户信息</t>
         </is>
       </c>
       <c r="E166" s="15" t="inlineStr">
         <is>
-          <t>🙋人工</t>
+          <t>🤖自动</t>
         </is>
       </c>
       <c r="F166" s="14" t="inlineStr">
         <is>
-          <t>已登录</t>
+          <t>后端运行中, 已登录</t>
         </is>
       </c>
       <c r="G166" s="14" t="inlineStr">
         <is>
-          <t>查看 Navbar</t>
+          <t>GET /api/v1/auth/me</t>
         </is>
       </c>
       <c r="H166" s="14" t="inlineStr">
         <is>
-          <t>显示昵称/邮箱 + '退出'</t>
+          <t>返回 email+nickname</t>
         </is>
       </c>
       <c r="I166" s="15" t="inlineStr"/>
@@ -9059,22 +9059,22 @@
     <row r="167" ht="32" customHeight="1">
       <c r="A167" s="15" t="inlineStr">
         <is>
-          <t>TC-9.2-07</t>
+          <t>TC-9.2-05</t>
         </is>
       </c>
       <c r="B167" s="15" t="inlineStr">
         <is>
-          <t>9.2 路由守卫 UI</t>
-        </is>
-      </c>
-      <c r="C167" s="17" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>9.2 认证 UI</t>
+        </is>
+      </c>
+      <c r="C167" s="18" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D167" s="14" t="inlineStr">
         <is>
-          <t>登录模态框切换</t>
+          <t>未登录显示登录按钮</t>
         </is>
       </c>
       <c r="E167" s="15" t="inlineStr">
@@ -9084,17 +9084,17 @@
       </c>
       <c r="F167" s="14" t="inlineStr">
         <is>
-          <t>未登录</t>
+          <t>前端运行, 未登录</t>
         </is>
       </c>
       <c r="G167" s="14" t="inlineStr">
         <is>
-          <t>登录→注册模式切换</t>
+          <t>查看 Navbar</t>
         </is>
       </c>
       <c r="H167" s="14" t="inlineStr">
         <is>
-          <t>表单切换，按钮文案变化</t>
+          <t>显示登录按钮</t>
         </is>
       </c>
       <c r="I167" s="15" t="inlineStr"/>
@@ -9108,42 +9108,42 @@
     <row r="168" ht="32" customHeight="1">
       <c r="A168" s="15" t="inlineStr">
         <is>
-          <t>TC-9.2-08</t>
+          <t>TC-9.2-06</t>
         </is>
       </c>
       <c r="B168" s="15" t="inlineStr">
         <is>
-          <t>9.2 路由守卫 UI</t>
-        </is>
-      </c>
-      <c r="C168" s="16" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>9.2 认证 UI</t>
+        </is>
+      </c>
+      <c r="C168" s="18" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D168" s="14" t="inlineStr">
         <is>
-          <t>登出后路由保护</t>
+          <t>已登录显示用户信息</t>
         </is>
       </c>
       <c r="E168" s="15" t="inlineStr">
         <is>
-          <t>🤖自动</t>
+          <t>🙋人工</t>
         </is>
       </c>
       <c r="F168" s="14" t="inlineStr">
         <is>
-          <t>已登录→登出</t>
+          <t>前端运行, 已登录</t>
         </is>
       </c>
       <c r="G168" s="14" t="inlineStr">
         <is>
-          <t>退出后访问 /search</t>
+          <t>查看 Navbar</t>
         </is>
       </c>
       <c r="H168" s="14" t="inlineStr">
         <is>
-          <t>重定向到 /login</t>
+          <t>显示昵称/邮箱+退出</t>
         </is>
       </c>
       <c r="I168" s="15" t="inlineStr"/>
@@ -9157,42 +9157,42 @@
     <row r="169" ht="32" customHeight="1">
       <c r="A169" s="15" t="inlineStr">
         <is>
-          <t>TC-9.3-01</t>
+          <t>TC-9.2-07</t>
         </is>
       </c>
       <c r="B169" s="15" t="inlineStr">
         <is>
-          <t>9.3 API 权限验证</t>
-        </is>
-      </c>
-      <c r="C169" s="16" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>9.2 认证 UI</t>
+        </is>
+      </c>
+      <c r="C169" s="18" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D169" s="14" t="inlineStr">
         <is>
-          <t>🔒 无Token访问聊天→401</t>
+          <t>登录/注册表单切换</t>
         </is>
       </c>
       <c r="E169" s="15" t="inlineStr">
         <is>
-          <t>🤖自动</t>
+          <t>🙋人工</t>
         </is>
       </c>
       <c r="F169" s="14" t="inlineStr">
         <is>
-          <t>未登录</t>
+          <t>前端运行</t>
         </is>
       </c>
       <c r="G169" s="14" t="inlineStr">
         <is>
-          <t>POST /api/v1/chat/messages</t>
+          <t>点击切换</t>
         </is>
       </c>
       <c r="H169" s="14" t="inlineStr">
         <is>
-          <t>返回 401</t>
+          <t>表单切换，按钮文案变化</t>
         </is>
       </c>
       <c r="I169" s="15" t="inlineStr"/>
@@ -9206,22 +9206,22 @@
     <row r="170" ht="32" customHeight="1">
       <c r="A170" s="15" t="inlineStr">
         <is>
-          <t>TC-9.3-02</t>
+          <t>TC-9.3-01</t>
         </is>
       </c>
       <c r="B170" s="15" t="inlineStr">
         <is>
-          <t>9.3 API 权限验证</t>
-        </is>
-      </c>
-      <c r="C170" s="17" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>9.3 API 权限</t>
+        </is>
+      </c>
+      <c r="C170" s="18" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D170" s="14" t="inlineStr">
         <is>
-          <t>🔒 无Token访问上传→401</t>
+          <t>聊天接口需认证</t>
         </is>
       </c>
       <c r="E170" s="15" t="inlineStr">
@@ -9231,17 +9231,17 @@
       </c>
       <c r="F170" s="14" t="inlineStr">
         <is>
-          <t>未登录</t>
+          <t>后端运行中</t>
         </is>
       </c>
       <c r="G170" s="14" t="inlineStr">
         <is>
-          <t>POST /api/v1/upload/report</t>
+          <t>POST /chat/messages 无Token</t>
         </is>
       </c>
       <c r="H170" s="14" t="inlineStr">
         <is>
-          <t>返回 401</t>
+          <t>返回401</t>
         </is>
       </c>
       <c r="I170" s="15" t="inlineStr"/>
@@ -9255,22 +9255,22 @@
     <row r="171" ht="32" customHeight="1">
       <c r="A171" s="15" t="inlineStr">
         <is>
-          <t>TC-9.3-03</t>
+          <t>TC-9.3-02</t>
         </is>
       </c>
       <c r="B171" s="15" t="inlineStr">
         <is>
-          <t>9.3 API 权限验证</t>
-        </is>
-      </c>
-      <c r="C171" s="17" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>9.3 API 权限</t>
+        </is>
+      </c>
+      <c r="C171" s="18" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D171" s="14" t="inlineStr">
         <is>
-          <t>🔒 无Token访问导出→401</t>
+          <t>上传接口需认证</t>
         </is>
       </c>
       <c r="E171" s="15" t="inlineStr">
@@ -9280,17 +9280,17 @@
       </c>
       <c r="F171" s="14" t="inlineStr">
         <is>
-          <t>未登录</t>
+          <t>后端运行中</t>
         </is>
       </c>
       <c r="G171" s="14" t="inlineStr">
         <is>
-          <t>POST /api/v1/export</t>
+          <t>POST /upload/report 无Token</t>
         </is>
       </c>
       <c r="H171" s="14" t="inlineStr">
         <is>
-          <t>返回 401</t>
+          <t>返回401</t>
         </is>
       </c>
       <c r="I171" s="15" t="inlineStr"/>
@@ -9304,22 +9304,22 @@
     <row r="172" ht="32" customHeight="1">
       <c r="A172" s="15" t="inlineStr">
         <is>
-          <t>TC-9.3-04</t>
+          <t>TC-9.3-03</t>
         </is>
       </c>
       <c r="B172" s="15" t="inlineStr">
         <is>
-          <t>9.3 API 权限验证</t>
-        </is>
-      </c>
-      <c r="C172" s="16" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>9.3 API 权限</t>
+        </is>
+      </c>
+      <c r="C172" s="18" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D172" s="14" t="inlineStr">
         <is>
-          <t>🔒 无Token访问历史→401</t>
+          <t>导出接口需认证</t>
         </is>
       </c>
       <c r="E172" s="15" t="inlineStr">
@@ -9329,17 +9329,17 @@
       </c>
       <c r="F172" s="14" t="inlineStr">
         <is>
-          <t>未登录</t>
+          <t>后端运行中</t>
         </is>
       </c>
       <c r="G172" s="14" t="inlineStr">
         <is>
-          <t>GET /api/v1/history</t>
+          <t>POST /export 无Token</t>
         </is>
       </c>
       <c r="H172" s="14" t="inlineStr">
         <is>
-          <t>返回 401</t>
+          <t>返回401</t>
         </is>
       </c>
       <c r="I172" s="15" t="inlineStr"/>
@@ -9353,22 +9353,22 @@
     <row r="173" ht="32" customHeight="1">
       <c r="A173" s="15" t="inlineStr">
         <is>
-          <t>TC-9.3-05</t>
+          <t>TC-9.3-04</t>
         </is>
       </c>
       <c r="B173" s="15" t="inlineStr">
         <is>
-          <t>9.3 API 权限验证</t>
-        </is>
-      </c>
-      <c r="C173" s="16" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>9.3 API 权限</t>
+        </is>
+      </c>
+      <c r="C173" s="18" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D173" s="14" t="inlineStr">
         <is>
-          <t>🔒 已登录正常访问</t>
+          <t>历史接口需认证</t>
         </is>
       </c>
       <c r="E173" s="15" t="inlineStr">
@@ -9378,17 +9378,17 @@
       </c>
       <c r="F173" s="14" t="inlineStr">
         <is>
-          <t>已登录带Token</t>
+          <t>后端运行中</t>
         </is>
       </c>
       <c r="G173" s="14" t="inlineStr">
         <is>
-          <t>GET /api/v1/history</t>
+          <t>GET /history 无Token</t>
         </is>
       </c>
       <c r="H173" s="14" t="inlineStr">
         <is>
-          <t>返回 200，数据正常</t>
+          <t>返回401</t>
         </is>
       </c>
       <c r="I173" s="15" t="inlineStr"/>
@@ -9402,22 +9402,22 @@
     <row r="174" ht="32" customHeight="1">
       <c r="A174" s="15" t="inlineStr">
         <is>
-          <t>TC-9.3-06</t>
+          <t>TC-9.3-05</t>
         </is>
       </c>
       <c r="B174" s="15" t="inlineStr">
         <is>
-          <t>9.3 API 权限验证</t>
-        </is>
-      </c>
-      <c r="C174" s="17" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>9.3 API 权限</t>
+        </is>
+      </c>
+      <c r="C174" s="18" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D174" s="14" t="inlineStr">
         <is>
-          <t>🔒 黑名单Token被拒</t>
+          <t>带Token访问历史</t>
         </is>
       </c>
       <c r="E174" s="15" t="inlineStr">
@@ -9427,17 +9427,17 @@
       </c>
       <c r="F174" s="14" t="inlineStr">
         <is>
-          <t>Token已登出</t>
+          <t>后端运行中, 已登录</t>
         </is>
       </c>
       <c r="G174" s="14" t="inlineStr">
         <is>
-          <t>用旧Token访问 🔒 接口</t>
+          <t>GET /history 带Token</t>
         </is>
       </c>
       <c r="H174" s="14" t="inlineStr">
         <is>
-          <t>返回 401</t>
+          <t>返回200</t>
         </is>
       </c>
       <c r="I174" s="15" t="inlineStr"/>
@@ -9456,17 +9456,17 @@
       </c>
       <c r="B175" s="15" t="inlineStr">
         <is>
-          <t>9.3 API 权限验证</t>
-        </is>
-      </c>
-      <c r="C175" s="16" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>9.3 API 权限</t>
+        </is>
+      </c>
+      <c r="C175" s="18" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D175" s="14" t="inlineStr">
         <is>
-          <t>🔓 公开接口无需Token</t>
+          <t>公开接口无需Token</t>
         </is>
       </c>
       <c r="E175" s="15" t="inlineStr">
@@ -9476,17 +9476,17 @@
       </c>
       <c r="F175" s="14" t="inlineStr">
         <is>
-          <t>未登录</t>
+          <t>后端运行中</t>
         </is>
       </c>
       <c r="G175" s="14" t="inlineStr">
         <is>
-          <t>GET /api/v1/search/companies?q=茅台</t>
+          <t>GET /search/companies 无Token</t>
         </is>
       </c>
       <c r="H175" s="14" t="inlineStr">
         <is>
-          <t>返回 200，正常数据</t>
+          <t>返回200</t>
         </is>
       </c>
       <c r="I175" s="15" t="inlineStr"/>
